--- a/PRONOSTICIINCORSO.xlsx
+++ b/PRONOSTICIINCORSO.xlsx
@@ -7,14 +7,15 @@
     <workbookView xWindow="480" yWindow="312" windowWidth="19872" windowHeight="7476"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="7" r:id="rId1"/>
+    <sheet name="TUTTOQUI" sheetId="7" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="189">
   <si>
     <t>G</t>
   </si>
@@ -609,6 +610,51 @@
   </si>
   <si>
     <t>7) TORINO - INTER</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>RISULTATI REALI</t>
+  </si>
+  <si>
+    <t>P1_RIS</t>
+  </si>
+  <si>
+    <t>P2_RIS</t>
+  </si>
+  <si>
+    <t>P3_RIS</t>
+  </si>
+  <si>
+    <t>P4_RIS</t>
+  </si>
+  <si>
+    <t>P5_RIS</t>
+  </si>
+  <si>
+    <t>P6_RIS</t>
+  </si>
+  <si>
+    <t>P7_RIS</t>
+  </si>
+  <si>
+    <t>P8_RIS</t>
+  </si>
+  <si>
+    <t>P9_RIS</t>
+  </si>
+  <si>
+    <t>P10_RIS</t>
   </si>
 </sst>
 </file>
@@ -828,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -896,6 +942,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1202,357 +1250,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y54"/>
+  <dimension ref="A1:Y56"/>
   <sheetFormatPr defaultColWidth="25.88671875" defaultRowHeight="21" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="A2" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="21" customHeight="1" thickBot="1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="5">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>2</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5">
-        <v>2</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" s="6"/>
-    </row>
-    <row r="3" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="9">
-        <v>2</v>
-      </c>
-      <c r="M3" s="9">
-        <v>1</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9">
-        <v>1</v>
-      </c>
-      <c r="P3" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>1</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="T3" s="9">
-        <v>2</v>
-      </c>
-      <c r="U3" s="9">
-        <v>1</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>0.75</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>0</v>
+      <c r="M4" s="5">
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="5">
-        <v>1</v>
-      </c>
-      <c r="S4" s="5">
-        <v>1</v>
-      </c>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
+      <c r="O4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>2</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="V4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="W4" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="X4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" s="11">
-        <v>0.5</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Y4" s="6"/>
     </row>
     <row r="5" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
+      <c r="L5" s="9">
+        <v>2</v>
+      </c>
+      <c r="M5" s="9">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>1</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="R5" s="9">
         <v>1</v>
       </c>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
+      <c r="S5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9">
+        <v>2</v>
+      </c>
+      <c r="U5" s="9">
+        <v>1</v>
+      </c>
       <c r="V5" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="W5" s="8" t="s">
         <v>49</v>
@@ -1561,65 +1546,69 @@
         <v>50</v>
       </c>
       <c r="Y5" s="10">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M6" s="6"/>
+        <v>37</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="N6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="S6" s="6"/>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>1</v>
+      </c>
       <c r="T6" s="6"/>
-      <c r="U6" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="U6" s="6"/>
       <c r="V6" s="4" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>49</v>
@@ -1627,29 +1616,31 @@
       <c r="X6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y6" s="6"/>
+      <c r="Y6" s="11">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>33</v>
@@ -1658,115 +1649,95 @@
         <v>34</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>70</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L7" s="12"/>
       <c r="M7" s="12"/>
-      <c r="N7" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9">
-        <v>1</v>
-      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
       <c r="P7" s="12"/>
-      <c r="Q7" s="8" t="s">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="12"/>
       <c r="R7" s="9">
         <v>1</v>
       </c>
-      <c r="S7" s="9">
-        <v>1</v>
-      </c>
+      <c r="S7" s="12"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y7" s="10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="5">
-        <v>2</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
-        <v>1</v>
-      </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5">
-        <v>1</v>
-      </c>
-      <c r="S8" s="5">
-        <v>1</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1</v>
-      </c>
-      <c r="U8" s="5">
-        <v>1</v>
+        <v>69</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="X8" s="4" t="s">
         <v>50</v>
@@ -1775,50 +1746,52 @@
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>48</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="N9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="O9" s="9">
         <v>1</v>
       </c>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
+      <c r="Q9" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="R9" s="9">
         <v>1</v>
       </c>
@@ -1826,17 +1799,15 @@
         <v>1</v>
       </c>
       <c r="T9" s="12"/>
-      <c r="U9" s="9">
-        <v>1</v>
-      </c>
+      <c r="U9" s="12"/>
       <c r="V9" s="8" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="W9" s="8" t="s">
         <v>39</v>
       </c>
       <c r="X9" s="8" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y9" s="10">
         <v>1</v>
@@ -1844,51 +1815,65 @@
     </row>
     <row r="10" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
       <c r="O10" s="5">
         <v>1</v>
       </c>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
+      <c r="P10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="R10" s="5">
         <v>1</v>
       </c>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
+      <c r="S10" s="5">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5">
+        <v>1</v>
+      </c>
       <c r="U10" s="5">
         <v>1</v>
       </c>
@@ -1896,74 +1881,74 @@
         <v>77</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="X10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y10" s="11">
-        <v>1</v>
-      </c>
+      <c r="Y10" s="6"/>
     </row>
     <row r="11" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O11" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="9">
+        <v>1</v>
+      </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
       <c r="R11" s="9">
         <v>1</v>
       </c>
-      <c r="S11" s="8" t="s">
-        <v>58</v>
+      <c r="S11" s="9">
+        <v>1</v>
       </c>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
+      <c r="U11" s="9">
+        <v>1</v>
+      </c>
       <c r="V11" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W11" s="8" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="X11" s="8" t="s">
         <v>50</v>
@@ -1974,183 +1959,179 @@
     </row>
     <row r="12" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L12" s="5">
-        <v>2</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="5">
         <v>1</v>
       </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="5">
-        <v>2</v>
-      </c>
+      <c r="Q12" s="6"/>
       <c r="R12" s="5">
         <v>1</v>
       </c>
-      <c r="S12" s="5">
-        <v>1</v>
-      </c>
+      <c r="S12" s="6"/>
       <c r="T12" s="6"/>
       <c r="U12" s="5">
         <v>1</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="X12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y12" s="6"/>
+      <c r="Y12" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>80</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>74</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="J13" s="8" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="L13" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="M13" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="9">
-        <v>1</v>
-      </c>
-      <c r="P13" s="9">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="9">
         <v>1</v>
       </c>
-      <c r="S13" s="9">
-        <v>1</v>
+      <c r="S13" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="T13" s="12"/>
-      <c r="U13" s="9">
-        <v>1</v>
-      </c>
+      <c r="U13" s="12"/>
       <c r="V13" s="8" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="W13" s="8" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="X13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y13" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>70</v>
+      <c r="L14" s="5">
+        <v>2</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
-      <c r="O14" s="4" t="s">
-        <v>58</v>
+      <c r="O14" s="5">
+        <v>1</v>
       </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="4" t="s">
-        <v>70</v>
+      <c r="Q14" s="5">
+        <v>2</v>
       </c>
       <c r="R14" s="5">
         <v>1</v>
@@ -2163,64 +2144,62 @@
         <v>1</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>0.5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Y14" s="6"/>
     </row>
     <row r="15" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>48</v>
       </c>
       <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O15" s="12"/>
+      <c r="M15" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="9">
+        <v>1</v>
+      </c>
       <c r="P15" s="9">
         <v>1</v>
       </c>
-      <c r="Q15" s="9">
-        <v>2</v>
-      </c>
+      <c r="Q15" s="12"/>
       <c r="R15" s="9">
         <v>1</v>
       </c>
@@ -2228,47 +2207,47 @@
         <v>1</v>
       </c>
       <c r="T15" s="12"/>
-      <c r="U15" s="8" t="s">
-        <v>0</v>
+      <c r="U15" s="9">
+        <v>1</v>
       </c>
       <c r="V15" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="W15" s="8" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="X15" s="8" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="Y15" s="12"/>
     </row>
     <row r="16" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A16" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>73</v>
@@ -2277,86 +2256,86 @@
         <v>48</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M16" s="6"/>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="6"/>
+      <c r="O16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O16" s="5">
-        <v>1</v>
-      </c>
       <c r="P16" s="6"/>
-      <c r="Q16" s="5">
-        <v>2</v>
+      <c r="Q16" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="R16" s="5">
         <v>1</v>
       </c>
-      <c r="S16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="S16" s="5">
+        <v>1</v>
+      </c>
+      <c r="T16" s="6"/>
       <c r="U16" s="5">
         <v>1</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y16" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="Y16" s="11">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="17" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A17" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="L17" s="12"/>
-      <c r="M17" s="9">
-        <v>1</v>
-      </c>
-      <c r="N17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="O17" s="12"/>
       <c r="P17" s="9">
         <v>1</v>
       </c>
-      <c r="Q17" s="12"/>
+      <c r="Q17" s="9">
+        <v>2</v>
+      </c>
       <c r="R17" s="9">
         <v>1</v>
       </c>
@@ -2364,62 +2343,64 @@
         <v>1</v>
       </c>
       <c r="T17" s="12"/>
-      <c r="U17" s="9">
-        <v>1</v>
+      <c r="U17" s="8" t="s">
+        <v>0</v>
       </c>
       <c r="V17" s="8" t="s">
         <v>104</v>
       </c>
       <c r="W17" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="X17" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y17" s="10">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Y17" s="12"/>
     </row>
     <row r="18" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A18" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>102</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="6"/>
+      <c r="L18" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="M18" s="6"/>
       <c r="N18" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O18" s="6"/>
+      <c r="O18" s="5">
+        <v>1</v>
+      </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="5">
         <v>2</v>
@@ -2427,69 +2408,69 @@
       <c r="R18" s="5">
         <v>1</v>
       </c>
-      <c r="S18" s="5">
-        <v>1</v>
-      </c>
-      <c r="T18" s="5">
-        <v>2</v>
-      </c>
-      <c r="U18" s="6"/>
+      <c r="S18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>1</v>
+      </c>
       <c r="V18" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="W18" s="4" t="s">
         <v>39</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y18" s="11">
-        <v>0.5</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y18" s="6"/>
     </row>
     <row r="19" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A19" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9">
-        <v>1</v>
-      </c>
-      <c r="P19" s="12"/>
+      <c r="M19" s="9">
+        <v>1</v>
+      </c>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="9">
+        <v>1</v>
+      </c>
       <c r="Q19" s="12"/>
       <c r="R19" s="9">
         <v>1</v>
@@ -2497,50 +2478,50 @@
       <c r="S19" s="9">
         <v>1</v>
       </c>
-      <c r="T19" s="9">
-        <v>2</v>
-      </c>
-      <c r="U19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="9">
+        <v>1</v>
+      </c>
       <c r="V19" s="8" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="W19" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="X19" s="8" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="Y19" s="10">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A20" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>47</v>
@@ -2553,53 +2534,55 @@
       <c r="N20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O20" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="O20" s="6"/>
       <c r="P20" s="6"/>
-      <c r="Q20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="R20" s="6"/>
-      <c r="S20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="T20" s="6"/>
-      <c r="U20" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="Q20" s="5">
+        <v>2</v>
+      </c>
+      <c r="R20" s="5">
+        <v>1</v>
+      </c>
+      <c r="S20" s="5">
+        <v>1</v>
+      </c>
+      <c r="T20" s="5">
+        <v>2</v>
+      </c>
+      <c r="U20" s="6"/>
       <c r="V20" s="4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="X20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y20" s="6"/>
+      <c r="Y20" s="11">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="21" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A21" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>89</v>
@@ -2608,89 +2591,93 @@
         <v>96</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="N21" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9">
+        <v>1</v>
+      </c>
+      <c r="P21" s="12"/>
       <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>58</v>
+      <c r="R21" s="9">
+        <v>1</v>
+      </c>
+      <c r="S21" s="9">
+        <v>1</v>
+      </c>
+      <c r="T21" s="9">
+        <v>2</v>
       </c>
       <c r="U21" s="12"/>
       <c r="V21" s="8" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="W21" s="8" t="s">
         <v>91</v>
       </c>
       <c r="X21" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y21" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="22" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A22" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="L22" s="6"/>
-      <c r="M22" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="M22" s="6"/>
       <c r="N22" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="5">
-        <v>1</v>
-      </c>
-      <c r="S22" s="5">
-        <v>1</v>
+      <c r="Q22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="R22" s="6"/>
+      <c r="S22" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="4" t="s">
@@ -2700,126 +2687,118 @@
         <v>91</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y22" s="11">
-        <v>0.5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Y22" s="6"/>
     </row>
     <row r="23" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A23" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L23" s="12"/>
-      <c r="M23" s="9">
-        <v>1</v>
-      </c>
-      <c r="N23" s="9">
-        <v>2</v>
-      </c>
-      <c r="O23" s="9">
-        <v>1</v>
-      </c>
-      <c r="P23" s="9">
-        <v>1</v>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="Q23" s="12"/>
-      <c r="R23" s="9">
-        <v>1</v>
-      </c>
-      <c r="S23" s="9">
-        <v>1</v>
-      </c>
-      <c r="T23" s="9">
-        <v>2</v>
-      </c>
-      <c r="U23" s="9">
-        <v>1</v>
-      </c>
+      <c r="R23" s="12"/>
+      <c r="S23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="T23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="U23" s="12"/>
       <c r="V23" s="8" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="W23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="X23" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="X23" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="Y23" s="12"/>
     </row>
     <row r="24" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5">
+        <v>1</v>
+      </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="5">
@@ -2829,17 +2808,17 @@
         <v>1</v>
       </c>
       <c r="T24" s="6"/>
-      <c r="U24" s="5">
-        <v>1</v>
+      <c r="U24" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="Y24" s="11">
         <v>0.5</v>
@@ -2847,109 +2826,115 @@
     </row>
     <row r="25" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A25" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>109</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12"/>
-      <c r="N25" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="R25" s="12"/>
-      <c r="S25" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
+        <v>121</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="9">
+        <v>1</v>
+      </c>
+      <c r="N25" s="9">
+        <v>2</v>
+      </c>
+      <c r="O25" s="9">
+        <v>1</v>
+      </c>
+      <c r="P25" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="9">
+        <v>1</v>
+      </c>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
+      <c r="T25" s="9">
+        <v>2</v>
+      </c>
+      <c r="U25" s="9">
+        <v>1</v>
+      </c>
       <c r="V25" s="8" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="X25" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y25" s="10">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Y25" s="12"/>
     </row>
     <row r="26" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A26" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="K26" s="4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="M26" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="5">
-        <v>1</v>
-      </c>
+      <c r="O26" s="6"/>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="5">
@@ -2959,9 +2944,11 @@
         <v>1</v>
       </c>
       <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
+      <c r="U26" s="5">
+        <v>1</v>
+      </c>
       <c r="V26" s="4" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="W26" s="4" t="s">
         <v>91</v>
@@ -2969,20 +2956,22 @@
       <c r="X26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y26" s="6"/>
+      <c r="Y26" s="11">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="27" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A27" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>74</v>
@@ -2991,120 +2980,106 @@
         <v>102</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L27" s="9">
-        <v>2</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12"/>
       <c r="N27" s="8" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
-      <c r="Q27" s="9">
-        <v>2</v>
-      </c>
-      <c r="R27" s="9">
-        <v>1</v>
-      </c>
-      <c r="S27" s="9">
-        <v>1</v>
+      <c r="Q27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="R27" s="12"/>
+      <c r="S27" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="T27" s="12"/>
       <c r="U27" s="12"/>
       <c r="V27" s="8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="W27" s="8" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="X27" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y27" s="12"/>
+        <v>99</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>70</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="L28" s="6"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="P28" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="5">
+        <v>1</v>
+      </c>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
       <c r="R28" s="5">
         <v>1</v>
       </c>
       <c r="S28" s="5">
         <v>1</v>
       </c>
-      <c r="T28" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="U28" s="5">
-        <v>1</v>
-      </c>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
       <c r="V28" s="4" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="W28" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="X28" s="4" t="s">
         <v>50</v>
@@ -3113,139 +3088,147 @@
     </row>
     <row r="29" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A29" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>102</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
+        <v>57</v>
+      </c>
+      <c r="L29" s="9">
+        <v>2</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="N29" s="8" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
+      <c r="Q29" s="9">
+        <v>2</v>
+      </c>
       <c r="R29" s="9">
         <v>1</v>
       </c>
       <c r="S29" s="9">
         <v>1</v>
       </c>
-      <c r="T29" s="9">
-        <v>2</v>
-      </c>
-      <c r="U29" s="9">
-        <v>1</v>
-      </c>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
       <c r="V29" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="W29" s="8" t="s">
         <v>49</v>
       </c>
       <c r="X29" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y29" s="10">
-        <v>0.5</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="Y29" s="12"/>
     </row>
     <row r="30" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A30" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L30" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="M30" s="6"/>
       <c r="N30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O30" s="5">
-        <v>1</v>
-      </c>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
+      <c r="O30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="R30" s="5">
         <v>1</v>
       </c>
       <c r="S30" s="5">
         <v>1</v>
       </c>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
+      <c r="T30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="U30" s="5">
+        <v>1</v>
+      </c>
       <c r="V30" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="W30" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="X30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y30" s="11">
-        <v>0.5</v>
-      </c>
+      <c r="Y30" s="6"/>
     </row>
     <row r="31" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A31" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>35</v>
@@ -3254,13 +3237,13 @@
         <v>73</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>32</v>
@@ -3269,34 +3252,34 @@
         <v>33</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O31" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="P31" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
-      <c r="R31" s="8" t="s">
-        <v>58</v>
+      <c r="R31" s="9">
+        <v>1</v>
       </c>
       <c r="S31" s="9">
         <v>1</v>
       </c>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
+      <c r="T31" s="9">
+        <v>2</v>
+      </c>
+      <c r="U31" s="9">
+        <v>1</v>
+      </c>
       <c r="V31" s="8" t="s">
         <v>49</v>
       </c>
@@ -3306,17 +3289,19 @@
       <c r="X31" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="Y31" s="12"/>
+      <c r="Y31" s="10">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="32" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A32" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>80</v>
@@ -3325,26 +3310,28 @@
         <v>74</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>48</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
+      <c r="N32" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="O32" s="5">
         <v>1</v>
       </c>
@@ -3359,22 +3346,24 @@
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
       <c r="V32" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="W32" s="4" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="X32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y32" s="6"/>
+      <c r="Y32" s="11">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="33" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A33" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>73</v>
@@ -3383,67 +3372,63 @@
         <v>80</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>37</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="L33" s="12"/>
       <c r="M33" s="12"/>
       <c r="N33" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="O33" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="P33" s="8" t="s">
         <v>58</v>
       </c>
       <c r="Q33" s="12"/>
       <c r="R33" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S33" s="12"/>
-      <c r="T33" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="U33" s="8" t="s">
-        <v>70</v>
-      </c>
+      <c r="S33" s="9">
+        <v>1</v>
+      </c>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
       <c r="V33" s="8" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="W33" s="8" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="X33" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y33" s="10">
-        <v>0.5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Y33" s="12"/>
     </row>
     <row r="34" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A34" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>28</v>
@@ -3455,49 +3440,41 @@
         <v>74</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>48</v>
       </c>
       <c r="L34" s="6"/>
-      <c r="M34" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="5">
+        <v>1</v>
+      </c>
       <c r="P34" s="6"/>
-      <c r="Q34" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="Q34" s="6"/>
       <c r="R34" s="5">
         <v>1</v>
       </c>
       <c r="S34" s="5">
         <v>1</v>
       </c>
-      <c r="T34" s="5">
-        <v>2</v>
-      </c>
-      <c r="U34" s="5">
-        <v>1</v>
-      </c>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
       <c r="V34" s="4" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="W34" s="4" t="s">
         <v>91</v>
@@ -3505,74 +3482,72 @@
       <c r="X34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y34" s="11">
-        <v>1</v>
-      </c>
+      <c r="Y34" s="6"/>
     </row>
     <row r="35" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A35" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>75</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>55</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L35" s="12"/>
+        <v>119</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="M35" s="12"/>
       <c r="N35" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O35" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O35" s="12"/>
+      <c r="P35" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="R35" s="9">
-        <v>1</v>
-      </c>
-      <c r="S35" s="9">
-        <v>1</v>
-      </c>
-      <c r="T35" s="12"/>
-      <c r="U35" s="9">
-        <v>1</v>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="S35" s="12"/>
+      <c r="T35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="U35" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="V35" s="8" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="W35" s="8" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="X35" s="8" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="Y35" s="10">
         <v>0.5</v>
@@ -3580,10 +3555,10 @@
     </row>
     <row r="36" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A36" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>28</v>
@@ -3595,47 +3570,49 @@
         <v>74</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>48</v>
       </c>
       <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="M36" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="N36" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="O36" s="5">
-        <v>1</v>
-      </c>
-      <c r="P36" s="5">
-        <v>1</v>
-      </c>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
       <c r="Q36" s="4" t="s">
         <v>0</v>
       </c>
       <c r="R36" s="5">
         <v>1</v>
       </c>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
+      <c r="S36" s="5">
+        <v>1</v>
+      </c>
+      <c r="T36" s="5">
+        <v>2</v>
+      </c>
       <c r="U36" s="5">
         <v>1</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="W36" s="4" t="s">
         <v>91</v>
@@ -3643,99 +3620,103 @@
       <c r="X36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y36" s="6"/>
+      <c r="Y36" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L37" s="12"/>
       <c r="M37" s="12"/>
       <c r="N37" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="O37" s="12"/>
+      <c r="O37" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
+      <c r="Q37" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="R37" s="9">
         <v>1</v>
       </c>
       <c r="S37" s="9">
         <v>1</v>
       </c>
-      <c r="T37" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>0</v>
+      <c r="T37" s="12"/>
+      <c r="U37" s="9">
+        <v>1</v>
       </c>
       <c r="V37" s="8" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="W37" s="8" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="X37" s="8" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="Y37" s="10">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>74</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>108</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>45</v>
@@ -3744,18 +3725,18 @@
         <v>68</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
-      <c r="N38" s="5">
-        <v>1</v>
+      <c r="N38" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="O38" s="5">
         <v>1</v>
       </c>
-      <c r="P38" s="4" t="s">
-        <v>0</v>
+      <c r="P38" s="5">
+        <v>1</v>
       </c>
       <c r="Q38" s="4" t="s">
         <v>0</v>
@@ -3763,71 +3744,63 @@
       <c r="R38" s="5">
         <v>1</v>
       </c>
-      <c r="S38" s="5">
-        <v>1</v>
-      </c>
+      <c r="S38" s="6"/>
       <c r="T38" s="6"/>
       <c r="U38" s="5">
         <v>1</v>
       </c>
       <c r="V38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W38" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="W38" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="X38" s="4" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="Y38" s="6"/>
     </row>
     <row r="39" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L39" s="9">
-        <v>2</v>
-      </c>
+      <c r="L39" s="12"/>
       <c r="M39" s="12"/>
       <c r="N39" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="O39" s="9">
-        <v>1</v>
-      </c>
-      <c r="P39" s="9">
-        <v>1</v>
-      </c>
+      <c r="O39" s="12"/>
+      <c r="P39" s="12"/>
       <c r="Q39" s="12"/>
       <c r="R39" s="9">
         <v>1</v>
@@ -3835,70 +3808,70 @@
       <c r="S39" s="9">
         <v>1</v>
       </c>
-      <c r="T39" s="12"/>
-      <c r="U39" s="9">
-        <v>1</v>
+      <c r="T39" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="U39" s="8" t="s">
+        <v>0</v>
       </c>
       <c r="V39" s="8" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="X39" s="8" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="Y39" s="10">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A40" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J40" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="L40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="P40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="5">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5">
+        <v>1</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="Q40" s="4" t="s">
         <v>0</v>
       </c>
@@ -3908,65 +3881,61 @@
       <c r="S40" s="5">
         <v>1</v>
       </c>
-      <c r="T40" s="5">
-        <v>2</v>
-      </c>
+      <c r="T40" s="6"/>
       <c r="U40" s="5">
         <v>1</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="Y40" s="6"/>
     </row>
     <row r="41" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A41" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="M41" s="9">
-        <v>1</v>
-      </c>
-      <c r="N41" s="9">
-        <v>1</v>
+        <v>48</v>
+      </c>
+      <c r="L41" s="9">
+        <v>2</v>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="8" t="s">
+        <v>0</v>
       </c>
       <c r="O41" s="9">
         <v>1</v>
@@ -3974,9 +3943,7 @@
       <c r="P41" s="9">
         <v>1</v>
       </c>
-      <c r="Q41" s="8" t="s">
-        <v>0</v>
-      </c>
+      <c r="Q41" s="12"/>
       <c r="R41" s="9">
         <v>1</v>
       </c>
@@ -3988,31 +3955,33 @@
         <v>1</v>
       </c>
       <c r="V41" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="W41" s="8" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="X41" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y41" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="Y41" s="10">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="42" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A42" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>48</v>
@@ -4021,28 +3990,30 @@
         <v>85</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>76</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="5">
-        <v>1</v>
-      </c>
-      <c r="P42" s="5">
-        <v>1</v>
-      </c>
+      <c r="M42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P42" s="6"/>
       <c r="Q42" s="4" t="s">
         <v>0</v>
       </c>
@@ -4055,55 +4026,53 @@
       <c r="T42" s="5">
         <v>2</v>
       </c>
-      <c r="U42" s="4" t="s">
-        <v>0</v>
+      <c r="U42" s="5">
+        <v>1</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="W42" s="4" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="X42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y42" s="11">
-        <v>0.75</v>
-      </c>
+      <c r="Y42" s="6"/>
     </row>
     <row r="43" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A43" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>48</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>0</v>
@@ -4111,8 +4080,8 @@
       <c r="M43" s="9">
         <v>1</v>
       </c>
-      <c r="N43" s="8" t="s">
-        <v>0</v>
+      <c r="N43" s="9">
+        <v>1</v>
       </c>
       <c r="O43" s="9">
         <v>1</v>
@@ -4120,8 +4089,8 @@
       <c r="P43" s="9">
         <v>1</v>
       </c>
-      <c r="Q43" s="9">
-        <v>2</v>
+      <c r="Q43" s="8" t="s">
+        <v>0</v>
       </c>
       <c r="R43" s="9">
         <v>1</v>
@@ -4129,134 +4098,142 @@
       <c r="S43" s="9">
         <v>1</v>
       </c>
-      <c r="T43" s="8" t="s">
-        <v>0</v>
-      </c>
+      <c r="T43" s="12"/>
       <c r="U43" s="9">
         <v>1</v>
       </c>
       <c r="V43" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="W43" s="8" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="X43" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y43" s="10">
-        <v>0.25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Y43" s="12"/>
     </row>
     <row r="44" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A44" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>74</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M44" s="6"/>
-      <c r="N44" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="5">
+        <v>1</v>
+      </c>
+      <c r="P44" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5">
+        <v>1</v>
+      </c>
+      <c r="S44" s="5">
+        <v>1</v>
+      </c>
+      <c r="T44" s="5">
+        <v>2</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="V44" s="4" t="s">
         <v>50</v>
       </c>
       <c r="W44" s="4" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="X44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y44" s="6"/>
+      <c r="Y44" s="11">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="45" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A45" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M45" s="9">
+        <v>1</v>
       </c>
       <c r="N45" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="O45" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="P45" s="8" t="s">
-        <v>0</v>
+      <c r="O45" s="9">
+        <v>1</v>
+      </c>
+      <c r="P45" s="9">
+        <v>1</v>
       </c>
       <c r="Q45" s="9">
         <v>2</v>
@@ -4270,83 +4247,77 @@
       <c r="T45" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="U45" s="8" t="s">
-        <v>70</v>
+      <c r="U45" s="9">
+        <v>1</v>
       </c>
       <c r="V45" s="8" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="W45" s="8" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="X45" s="8" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="Y45" s="10">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A46" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="M46" s="6"/>
       <c r="N46" s="4" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
-      <c r="R46" s="5">
-        <v>1</v>
-      </c>
-      <c r="S46" s="5">
-        <v>1</v>
-      </c>
-      <c r="T46" s="5">
-        <v>2</v>
-      </c>
-      <c r="U46" s="5">
-        <v>1</v>
-      </c>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6"/>
+      <c r="U46" s="6"/>
       <c r="V46" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W46" s="4" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="X46" s="4" t="s">
         <v>40</v>
@@ -4355,90 +4326,102 @@
     </row>
     <row r="47" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A47" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>114</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O47" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P47" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>2</v>
+      </c>
       <c r="R47" s="9">
         <v>1</v>
       </c>
       <c r="S47" s="9">
         <v>1</v>
       </c>
-      <c r="T47" s="9">
-        <v>2</v>
-      </c>
-      <c r="U47" s="9">
-        <v>1</v>
+      <c r="T47" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="U47" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="V47" s="8" t="s">
         <v>49</v>
       </c>
       <c r="W47" s="8" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="X47" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="Y47" s="10">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A48" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>33</v>
@@ -4447,132 +4430,130 @@
         <v>96</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
-      <c r="N48" s="5">
-        <v>1</v>
-      </c>
-      <c r="O48" s="5">
-        <v>1</v>
+      <c r="N48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="P48" s="6"/>
-      <c r="Q48" s="5">
+      <c r="Q48" s="6"/>
+      <c r="R48" s="5">
+        <v>1</v>
+      </c>
+      <c r="S48" s="5">
+        <v>1</v>
+      </c>
+      <c r="T48" s="5">
         <v>2</v>
       </c>
-      <c r="R48" s="5">
-        <v>1</v>
-      </c>
-      <c r="S48" s="5">
-        <v>1</v>
-      </c>
-      <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
+      <c r="U48" s="5">
+        <v>1</v>
+      </c>
       <c r="V48" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="W48" s="4" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="X48" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y48" s="11">
-        <v>0.5</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Y48" s="6"/>
     </row>
     <row r="49" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A49" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>70</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="L49" s="12"/>
       <c r="M49" s="12"/>
-      <c r="N49" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="O49" s="9">
-        <v>1</v>
-      </c>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
       <c r="P49" s="12"/>
-      <c r="Q49" s="8" t="s">
-        <v>0</v>
-      </c>
+      <c r="Q49" s="12"/>
       <c r="R49" s="9">
         <v>1</v>
       </c>
       <c r="S49" s="9">
         <v>1</v>
       </c>
-      <c r="T49" s="12"/>
-      <c r="U49" s="12"/>
+      <c r="T49" s="9">
+        <v>2</v>
+      </c>
+      <c r="U49" s="9">
+        <v>1</v>
+      </c>
       <c r="V49" s="8" t="s">
         <v>49</v>
       </c>
       <c r="W49" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="X49" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y49" s="12"/>
+        <v>77</v>
+      </c>
+      <c r="Y49" s="10">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="50" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A50" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>33</v>
@@ -4581,26 +4562,22 @@
         <v>96</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L50" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>58</v>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="5">
+        <v>1</v>
       </c>
       <c r="O50" s="5">
         <v>1</v>
       </c>
       <c r="P50" s="6"/>
-      <c r="Q50" s="4" t="s">
-        <v>0</v>
+      <c r="Q50" s="5">
+        <v>2</v>
       </c>
       <c r="R50" s="5">
         <v>1</v>
@@ -4609,91 +4586,81 @@
         <v>1</v>
       </c>
       <c r="T50" s="6"/>
-      <c r="U50" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="U50" s="6"/>
       <c r="V50" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="W50" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X50" s="4" t="s">
         <v>50</v>
       </c>
       <c r="Y50" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A51" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="M51" s="9">
-        <v>1</v>
-      </c>
-      <c r="N51" s="9">
-        <v>2</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="P51" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>2</v>
-      </c>
-      <c r="R51" s="8" t="s">
-        <v>58</v>
+        <v>70</v>
+      </c>
+      <c r="M51" s="12"/>
+      <c r="N51" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O51" s="9">
+        <v>1</v>
+      </c>
+      <c r="P51" s="12"/>
+      <c r="Q51" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R51" s="9">
+        <v>1</v>
       </c>
       <c r="S51" s="9">
         <v>1</v>
       </c>
-      <c r="T51" s="9">
-        <v>2</v>
-      </c>
-      <c r="U51" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="T51" s="12"/>
+      <c r="U51" s="12"/>
       <c r="V51" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="W51" s="8" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="X51" s="8" t="s">
         <v>50</v>
@@ -4701,218 +4668,375 @@
       <c r="Y51" s="12"/>
     </row>
     <row r="52" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A52" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O52" s="5">
+        <v>1</v>
+      </c>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5">
+        <v>1</v>
+      </c>
+      <c r="S52" s="5">
+        <v>1</v>
+      </c>
+      <c r="T52" s="6"/>
+      <c r="U52" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X52" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y52" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" ht="21" customHeight="1" thickBot="1">
+      <c r="A53" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F52" s="14" t="s">
+      <c r="C53" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="K53" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G52" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I52" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="L52" s="15">
+      <c r="L53" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M53" s="9">
+        <v>1</v>
+      </c>
+      <c r="N53" s="9">
         <v>2</v>
       </c>
-      <c r="M52" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="N52" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="O52" s="15">
-        <v>1</v>
-      </c>
-      <c r="P52" s="15">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="15">
+      <c r="O53" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="P53" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="9">
         <v>2</v>
       </c>
-      <c r="R52" s="15">
-        <v>1</v>
-      </c>
-      <c r="S52" s="15">
-        <v>1</v>
-      </c>
-      <c r="T52" s="14" t="s">
+      <c r="R53" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="U52" s="15">
-        <v>1</v>
-      </c>
-      <c r="V52" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="W52" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="X52" s="14" t="s">
+      <c r="S53" s="9">
+        <v>1</v>
+      </c>
+      <c r="T53" s="9">
+        <v>2</v>
+      </c>
+      <c r="U53" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="V53" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="Y52" s="6"/>
-    </row>
-    <row r="53" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A53" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="G53" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="I53" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="J53" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="K53" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="L53" s="18">
-        <v>1</v>
-      </c>
-      <c r="M53" s="19"/>
-      <c r="N53" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="O53" s="18">
-        <v>2</v>
-      </c>
-      <c r="P53" s="19"/>
-      <c r="Q53" s="18">
-        <v>2</v>
-      </c>
-      <c r="R53" s="18">
-        <v>2</v>
-      </c>
-      <c r="S53" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="T53" s="19"/>
-      <c r="U53" s="19"/>
-      <c r="V53" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="W53" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="X53" s="20" t="s">
-        <v>167</v>
+      <c r="W53" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="X53" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="Y53" s="12"/>
     </row>
     <row r="54" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A54" s="13" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L54" s="15">
-        <v>1</v>
-      </c>
-      <c r="M54" s="15">
-        <v>1</v>
-      </c>
-      <c r="N54" s="15">
         <v>2</v>
       </c>
-      <c r="O54" s="21"/>
-      <c r="P54" s="21"/>
+      <c r="M54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O54" s="15">
+        <v>1</v>
+      </c>
+      <c r="P54" s="15">
+        <v>1</v>
+      </c>
       <c r="Q54" s="15">
         <v>2</v>
       </c>
       <c r="R54" s="15">
+        <v>1</v>
+      </c>
+      <c r="S54" s="15">
+        <v>1</v>
+      </c>
+      <c r="T54" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="U54" s="15">
+        <v>1</v>
+      </c>
+      <c r="V54" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="W54" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="X54" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y54" s="6"/>
+    </row>
+    <row r="55" spans="1:25" ht="21" customHeight="1" thickBot="1">
+      <c r="A55" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="J55" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L55" s="18">
+        <v>1</v>
+      </c>
+      <c r="M55" s="19"/>
+      <c r="N55" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="O55" s="18">
         <v>2</v>
       </c>
-      <c r="S54" s="15">
-        <v>1</v>
-      </c>
-      <c r="T54" s="15">
+      <c r="P55" s="19"/>
+      <c r="Q55" s="18">
         <v>2</v>
       </c>
-      <c r="U54" s="21"/>
-      <c r="V54" s="14" t="s">
+      <c r="R55" s="18">
+        <v>2</v>
+      </c>
+      <c r="S55" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="T55" s="19"/>
+      <c r="U55" s="19"/>
+      <c r="V55" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="W55" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="X55" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y55" s="12"/>
+    </row>
+    <row r="56" spans="1:25" ht="21" customHeight="1" thickBot="1">
+      <c r="A56" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J56" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L56" s="15">
+        <v>1</v>
+      </c>
+      <c r="M56" s="15">
+        <v>1</v>
+      </c>
+      <c r="N56" s="15">
+        <v>2</v>
+      </c>
+      <c r="O56" s="21"/>
+      <c r="P56" s="21"/>
+      <c r="Q56" s="15">
+        <v>2</v>
+      </c>
+      <c r="R56" s="15">
+        <v>2</v>
+      </c>
+      <c r="S56" s="15">
+        <v>1</v>
+      </c>
+      <c r="T56" s="15">
+        <v>2</v>
+      </c>
+      <c r="U56" s="21"/>
+      <c r="V56" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="W54" s="14" t="s">
+      <c r="W56" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="X54" s="14" t="s">
+      <c r="X56" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="Y54" s="22"/>
+      <c r="Y56" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PRONOSTICIINCORSO.xlsx
+++ b/PRONOSTICIINCORSO.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="188">
   <si>
     <t>G</t>
   </si>
@@ -622,9 +622,6 @@
   </si>
   <si>
     <t>1-1</t>
-  </si>
-  <si>
-    <t>RISULTATI REALI</t>
   </si>
   <si>
     <t>P1_RIS</t>
@@ -1254,41 +1251,41 @@
   <sheetFormatPr defaultColWidth="25.88671875" defaultRowHeight="21" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>188</v>
-      </c>
     </row>
     <row r="2" spans="1:25" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="23" t="s">
-        <v>178</v>
-      </c>
       <c r="B2" s="23" t="s">
         <v>174</v>
       </c>
@@ -1321,9 +1318,7 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
